--- a/tests/fixtures/sample_qualtrics.xlsx
+++ b/tests/fixtures/sample_qualtrics.xlsx
@@ -1,152 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jbenas\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E14719C3-C042-4629-B09A-66F6EC6EC085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet0!$A$1:$X$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet0'!$A$1:$X$3</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
-  <si>
-    <t>Progress</t>
-  </si>
-  <si>
-    <t>Duration (in seconds)</t>
-  </si>
-  <si>
-    <t>Finished</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>Response Type</t>
-  </si>
-  <si>
-    <t>IP Address</t>
-  </si>
-  <si>
-    <t>Recorded Date</t>
-  </si>
-  <si>
-    <t>Response ID</t>
-  </si>
-  <si>
-    <t>Recipient Last Name</t>
-  </si>
-  <si>
-    <t>Recipient First Name</t>
-  </si>
-  <si>
-    <t>Recipient Email</t>
-  </si>
-  <si>
-    <t>External Data Reference</t>
-  </si>
-  <si>
-    <t>Location Latitude</t>
-  </si>
-  <si>
-    <t>Location Longitude</t>
-  </si>
-  <si>
-    <t>Distribution Channel</t>
-  </si>
-  <si>
-    <t>User Language</t>
-  </si>
-  <si>
-    <t>Name (as you would like it to appear on your CE certificate):</t>
-  </si>
-  <si>
-    <t>Preferred email address:</t>
-  </si>
-  <si>
-    <t>Type of CE credit needed:
-(please note that the below options represent available CEs across all GSAPP offerings. Not all options may apply to the specific training you attended. Please review that training's webpage to see all available CEs for that training.) - Selected Choice</t>
-  </si>
-  <si>
-    <t>Type of CE credit needed:
-(please note that the below options represent available CEs across all GSAPP offerings. Not all options may apply to the specific training you attended. Please review that training's webpage to see all available CEs for that training.) - Psychologist (New York) (please enter license #) - Text</t>
-  </si>
-  <si>
-    <t>Type of CE credit needed:
-(please note that the below options represent available CEs across all GSAPP offerings. Not all options may apply to the specific training you attended. Please review that training's webpage to see all available CEs for that training.) - BCBA (please enter certificate #) - Text</t>
-  </si>
-  <si>
-    <t>To be informed of future events through our listserv, please re-enter your email below:</t>
-  </si>
-  <si>
-    <t>Are you interested in having GSAPP provide an in-service training or consultation for your organization? 
-If yes, we will email you to follow-up.</t>
-  </si>
-  <si>
-    <t>128.6.36.9</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>R_5fE5nnGye7kfMFl</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>anonymous</t>
-  </si>
-  <si>
-    <t>EN</t>
-  </si>
-  <si>
-    <t>Jessica Benas</t>
-  </si>
-  <si>
-    <t>jbenas@gsapp.rutgers.edu</t>
-  </si>
-  <si>
-    <t>Psychologist (APA)</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -169,27 +54,87 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -509,163 +454,394 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X2"/>
-  <sheetFormatPr defaultColWidth="20.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="20.6328125" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="3" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Response Type</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Duration (in seconds)</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Recorded Date</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Response ID</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Recipient Last Name</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Recipient First Name</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Recipient Email</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>External Data Reference</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Location Latitude</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Location Longitude</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Distribution Channel</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>User Language</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Name (as you would like it to appear on your CE certificate):</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Preferred email address:</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Type of CE credit needed:
+(please note that the below options represent available CEs across all GSAPP offerings. Not all options may apply to the specific training you attended. Please review that training's webpage to see all available CEs for that training.) - Selected Choice</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Type of CE credit needed:
+(please note that the below options represent available CEs across all GSAPP offerings. Not all options may apply to the specific training you attended. Please review that training's webpage to see all available CEs for that training.) - Psychologist (New York) (please enter license #) - Text</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Type of CE credit needed:
+(please note that the below options represent available CEs across all GSAPP offerings. Not all options may apply to the specific training you attended. Please review that training's webpage to see all available CEs for that training.) - BCBA (please enter certificate #) - Text</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>To be informed of future events through our listserv, please re-enter your email below:</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Are you interested in having GSAPP provide an in-service training or consultation for your organization? 
+If yes, we will email you to follow-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="1" t="n">
+        <v>46189.57310185185</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46189.57333333333</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>128.6.36.9</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>23</v>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>46189.57334582176</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>R_5fE5nnGye7kfMFl</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>40.5511</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-74.4606</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Jessica Benas</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>jbenas@gsapp.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>Psychologist (APA)</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>jbenas@gsapp.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>46189.573101851849</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46189.573333333334</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2">
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46189.57310185185</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>46189.57333333333</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>128.6.36.9</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>100</v>
       </c>
-      <c r="F2">
+      <c r="F3" t="n">
         <v>20</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="1">
-        <v>46189.573345821758</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2">
-        <v>40.551099999999998</v>
-      </c>
-      <c r="O2">
-        <v>-74.460599999999999</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>33</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>46189.57334582176</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>R_5fE5nnGye7kfMFl</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>40.5511</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-74.4606</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Hannah Lee</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>hannah@example.com</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Psychologist (APA)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>jbenas@gsapp.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46189.57310185185</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>46189.57333333333</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>128.6.36.9</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>46189.57334582176</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>R_5fE5nnGye7kfMFl</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>40.5511</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-74.4606</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Cara Laitusis</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>cara@example.com</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>National Association of School Psychologists (NASP)</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>jbenas@gsapp.rutgers.edu</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="C1:C2 D1:D2 G1:G2 I1:I2 J1:J2 K1:K2 L1:L2 M1:M2 P1:P2 Q1:Q2 R1:R2 S1:S2 T1:T2 U1:U2 V1:V2 W1:W2 X1:X2" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>